--- a/excel/TradeMind_Appium_500_Report.xlsx
+++ b/excel/TradeMind_Appium_500_Report.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2532" uniqueCount="1032">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2532" uniqueCount="1033">
   <si>
     <t>Category / Metric</t>
   </si>
@@ -56,7 +56,7 @@
     <t>Report Timestamp</t>
   </si>
   <si>
-    <t>2026-07-31T05:05:16.706Z</t>
+    <t>2026-07-31T05:17:35.756Z</t>
   </si>
   <si>
     <t>Module Name</t>
@@ -1056,6 +1056,9 @@
   </si>
   <si>
     <t>TC_APM_HW_008</t>
+  </si>
+  <si>
+    <t>Device Accelerometer Sensor Orientation Change Listener (Portrait vs Landscape)</t>
   </si>
   <si>
     <t>TC_APM_HW_009</t>
@@ -6362,7 +6365,7 @@
         <v>20</v>
       </c>
       <c r="C159" t="s">
-        <v>58</v>
+        <v>348</v>
       </c>
       <c r="D159" t="s">
         <v>33</v>
@@ -6373,13 +6376,13 @@
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B160" t="s">
         <v>20</v>
       </c>
       <c r="C160" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D160" t="s">
         <v>33</v>
@@ -6390,13 +6393,13 @@
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B161" t="s">
         <v>20</v>
       </c>
       <c r="C161" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D161" t="s">
         <v>33</v>
@@ -6407,13 +6410,13 @@
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B162" t="s">
         <v>20</v>
       </c>
       <c r="C162" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D162" t="s">
         <v>33</v>
@@ -6424,13 +6427,13 @@
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B163" t="s">
         <v>20</v>
       </c>
       <c r="C163" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D163" t="s">
         <v>33</v>
@@ -6441,13 +6444,13 @@
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B164" t="s">
         <v>20</v>
       </c>
       <c r="C164" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D164" t="s">
         <v>33</v>
@@ -6458,13 +6461,13 @@
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B165" t="s">
         <v>20</v>
       </c>
       <c r="C165" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D165" t="s">
         <v>33</v>
@@ -6475,13 +6478,13 @@
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B166" t="s">
         <v>20</v>
       </c>
       <c r="C166" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D166" t="s">
         <v>33</v>
@@ -6492,13 +6495,13 @@
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B167" t="s">
         <v>20</v>
       </c>
       <c r="C167" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D167" t="s">
         <v>33</v>
@@ -6509,13 +6512,13 @@
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B168" t="s">
         <v>20</v>
       </c>
       <c r="C168" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D168" t="s">
         <v>33</v>
@@ -6526,13 +6529,13 @@
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B169" t="s">
         <v>20</v>
       </c>
       <c r="C169" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D169" t="s">
         <v>33</v>
@@ -6543,13 +6546,13 @@
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B170" t="s">
         <v>20</v>
       </c>
       <c r="C170" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="D170" t="s">
         <v>33</v>
@@ -6560,13 +6563,13 @@
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B171" t="s">
         <v>20</v>
       </c>
       <c r="C171" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D171" t="s">
         <v>33</v>
@@ -6577,13 +6580,13 @@
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B172" t="s">
         <v>20</v>
       </c>
       <c r="C172" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D172" t="s">
         <v>33</v>
@@ -6594,13 +6597,13 @@
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B173" t="s">
         <v>20</v>
       </c>
       <c r="C173" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D173" t="s">
         <v>33</v>
@@ -6611,13 +6614,13 @@
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B174" t="s">
         <v>20</v>
       </c>
       <c r="C174" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D174" t="s">
         <v>33</v>
@@ -6628,13 +6631,13 @@
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B175" t="s">
         <v>20</v>
       </c>
       <c r="C175" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D175" t="s">
         <v>33</v>
@@ -6645,13 +6648,13 @@
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B176" t="s">
         <v>20</v>
       </c>
       <c r="C176" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D176" t="s">
         <v>33</v>
@@ -6662,13 +6665,13 @@
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B177" t="s">
         <v>20</v>
       </c>
       <c r="C177" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D177" t="s">
         <v>33</v>
@@ -6679,13 +6682,13 @@
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B178" t="s">
         <v>20</v>
       </c>
       <c r="C178" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D178" t="s">
         <v>33</v>
@@ -6696,13 +6699,13 @@
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B179" t="s">
         <v>20</v>
       </c>
       <c r="C179" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D179" t="s">
         <v>33</v>
@@ -6713,13 +6716,13 @@
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B180" t="s">
         <v>20</v>
       </c>
       <c r="C180" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D180" t="s">
         <v>33</v>
@@ -6730,13 +6733,13 @@
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B181" t="s">
         <v>20</v>
       </c>
       <c r="C181" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D181" t="s">
         <v>33</v>
@@ -6747,13 +6750,13 @@
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B182" t="s">
         <v>20</v>
       </c>
       <c r="C182" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="D182" t="s">
         <v>33</v>
@@ -6764,13 +6767,13 @@
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B183" t="s">
         <v>20</v>
       </c>
       <c r="C183" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="D183" t="s">
         <v>33</v>
@@ -6781,13 +6784,13 @@
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B184" t="s">
         <v>20</v>
       </c>
       <c r="C184" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D184" t="s">
         <v>33</v>
@@ -6798,13 +6801,13 @@
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B185" t="s">
         <v>20</v>
       </c>
       <c r="C185" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D185" t="s">
         <v>33</v>
@@ -6815,13 +6818,13 @@
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B186" t="s">
         <v>20</v>
       </c>
       <c r="C186" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="D186" t="s">
         <v>33</v>
@@ -6832,13 +6835,13 @@
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B187" t="s">
         <v>20</v>
       </c>
       <c r="C187" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="D187" t="s">
         <v>33</v>
@@ -6849,13 +6852,13 @@
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B188" t="s">
         <v>20</v>
       </c>
       <c r="C188" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D188" t="s">
         <v>33</v>
@@ -6866,13 +6869,13 @@
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B189" t="s">
         <v>20</v>
       </c>
       <c r="C189" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D189" t="s">
         <v>33</v>
@@ -6883,13 +6886,13 @@
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B190" t="s">
         <v>20</v>
       </c>
       <c r="C190" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="D190" t="s">
         <v>33</v>
@@ -6900,13 +6903,13 @@
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B191" t="s">
         <v>20</v>
       </c>
       <c r="C191" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="D191" t="s">
         <v>33</v>
@@ -6917,13 +6920,13 @@
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B192" t="s">
         <v>20</v>
       </c>
       <c r="C192" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D192" t="s">
         <v>33</v>
@@ -6934,13 +6937,13 @@
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B193" t="s">
         <v>20</v>
       </c>
       <c r="C193" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="D193" t="s">
         <v>33</v>
@@ -6951,13 +6954,13 @@
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B194" t="s">
         <v>20</v>
       </c>
       <c r="C194" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="D194" t="s">
         <v>33</v>
@@ -6968,13 +6971,13 @@
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B195" t="s">
         <v>20</v>
       </c>
       <c r="C195" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D195" t="s">
         <v>33</v>
@@ -6985,13 +6988,13 @@
     </row>
     <row r="196" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B196" t="s">
         <v>20</v>
       </c>
       <c r="C196" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D196" t="s">
         <v>33</v>
@@ -7002,13 +7005,13 @@
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B197" t="s">
         <v>20</v>
       </c>
       <c r="C197" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D197" t="s">
         <v>33</v>
@@ -7019,13 +7022,13 @@
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B198" t="s">
         <v>20</v>
       </c>
       <c r="C198" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D198" t="s">
         <v>33</v>
@@ -7036,13 +7039,13 @@
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B199" t="s">
         <v>20</v>
       </c>
       <c r="C199" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D199" t="s">
         <v>33</v>
@@ -7053,13 +7056,13 @@
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B200" t="s">
         <v>20</v>
       </c>
       <c r="C200" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D200" t="s">
         <v>33</v>
@@ -7070,13 +7073,13 @@
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B201" t="s">
         <v>20</v>
       </c>
       <c r="C201" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D201" t="s">
         <v>33</v>
@@ -7087,13 +7090,13 @@
     </row>
     <row r="202" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B202" t="s">
         <v>21</v>
       </c>
       <c r="C202" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="D202" t="s">
         <v>33</v>
@@ -7104,13 +7107,13 @@
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B203" t="s">
         <v>21</v>
       </c>
       <c r="C203" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="D203" t="s">
         <v>33</v>
@@ -7121,13 +7124,13 @@
     </row>
     <row r="204" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B204" t="s">
         <v>21</v>
       </c>
       <c r="C204" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="D204" t="s">
         <v>33</v>
@@ -7138,13 +7141,13 @@
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B205" t="s">
         <v>21</v>
       </c>
       <c r="C205" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="D205" t="s">
         <v>33</v>
@@ -7155,13 +7158,13 @@
     </row>
     <row r="206" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B206" t="s">
         <v>21</v>
       </c>
       <c r="C206" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D206" t="s">
         <v>33</v>
@@ -7172,13 +7175,13 @@
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B207" t="s">
         <v>21</v>
       </c>
       <c r="C207" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D207" t="s">
         <v>33</v>
@@ -7189,13 +7192,13 @@
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B208" t="s">
         <v>21</v>
       </c>
       <c r="C208" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="D208" t="s">
         <v>33</v>
@@ -7206,13 +7209,13 @@
     </row>
     <row r="209" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B209" t="s">
         <v>21</v>
       </c>
       <c r="C209" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D209" t="s">
         <v>33</v>
@@ -7223,13 +7226,13 @@
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B210" t="s">
         <v>21</v>
       </c>
       <c r="C210" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="D210" t="s">
         <v>33</v>
@@ -7240,13 +7243,13 @@
     </row>
     <row r="211" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B211" t="s">
         <v>21</v>
       </c>
       <c r="C211" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="D211" t="s">
         <v>33</v>
@@ -7257,13 +7260,13 @@
     </row>
     <row r="212" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B212" t="s">
         <v>21</v>
       </c>
       <c r="C212" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="D212" t="s">
         <v>33</v>
@@ -7274,13 +7277,13 @@
     </row>
     <row r="213" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B213" t="s">
         <v>21</v>
       </c>
       <c r="C213" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="D213" t="s">
         <v>33</v>
@@ -7291,13 +7294,13 @@
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B214" t="s">
         <v>21</v>
       </c>
       <c r="C214" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D214" t="s">
         <v>33</v>
@@ -7308,13 +7311,13 @@
     </row>
     <row r="215" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B215" t="s">
         <v>21</v>
       </c>
       <c r="C215" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="D215" t="s">
         <v>33</v>
@@ -7325,13 +7328,13 @@
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B216" t="s">
         <v>21</v>
       </c>
       <c r="C216" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="D216" t="s">
         <v>33</v>
@@ -7342,13 +7345,13 @@
     </row>
     <row r="217" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B217" t="s">
         <v>21</v>
       </c>
       <c r="C217" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="D217" t="s">
         <v>33</v>
@@ -7359,13 +7362,13 @@
     </row>
     <row r="218" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B218" t="s">
         <v>21</v>
       </c>
       <c r="C218" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="D218" t="s">
         <v>33</v>
@@ -7376,13 +7379,13 @@
     </row>
     <row r="219" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B219" t="s">
         <v>21</v>
       </c>
       <c r="C219" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="D219" t="s">
         <v>33</v>
@@ -7393,13 +7396,13 @@
     </row>
     <row r="220" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B220" t="s">
         <v>21</v>
       </c>
       <c r="C220" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="D220" t="s">
         <v>33</v>
@@ -7410,13 +7413,13 @@
     </row>
     <row r="221" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B221" t="s">
         <v>21</v>
       </c>
       <c r="C221" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="D221" t="s">
         <v>33</v>
@@ -7427,13 +7430,13 @@
     </row>
     <row r="222" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B222" t="s">
         <v>21</v>
       </c>
       <c r="C222" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="D222" t="s">
         <v>33</v>
@@ -7444,13 +7447,13 @@
     </row>
     <row r="223" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B223" t="s">
         <v>21</v>
       </c>
       <c r="C223" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="D223" t="s">
         <v>33</v>
@@ -7461,13 +7464,13 @@
     </row>
     <row r="224" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B224" t="s">
         <v>21</v>
       </c>
       <c r="C224" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="D224" t="s">
         <v>33</v>
@@ -7478,13 +7481,13 @@
     </row>
     <row r="225" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B225" t="s">
         <v>21</v>
       </c>
       <c r="C225" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="D225" t="s">
         <v>33</v>
@@ -7495,13 +7498,13 @@
     </row>
     <row r="226" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B226" t="s">
         <v>21</v>
       </c>
       <c r="C226" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="D226" t="s">
         <v>33</v>
@@ -7512,13 +7515,13 @@
     </row>
     <row r="227" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B227" t="s">
         <v>21</v>
       </c>
       <c r="C227" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="D227" t="s">
         <v>33</v>
@@ -7529,13 +7532,13 @@
     </row>
     <row r="228" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B228" t="s">
         <v>21</v>
       </c>
       <c r="C228" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="D228" t="s">
         <v>33</v>
@@ -7546,13 +7549,13 @@
     </row>
     <row r="229" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B229" t="s">
         <v>21</v>
       </c>
       <c r="C229" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="D229" t="s">
         <v>33</v>
@@ -7563,13 +7566,13 @@
     </row>
     <row r="230" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B230" t="s">
         <v>21</v>
       </c>
       <c r="C230" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="D230" t="s">
         <v>33</v>
@@ -7580,13 +7583,13 @@
     </row>
     <row r="231" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B231" t="s">
         <v>21</v>
       </c>
       <c r="C231" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="D231" t="s">
         <v>33</v>
@@ -7597,13 +7600,13 @@
     </row>
     <row r="232" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B232" t="s">
         <v>21</v>
       </c>
       <c r="C232" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="D232" t="s">
         <v>33</v>
@@ -7614,13 +7617,13 @@
     </row>
     <row r="233" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B233" t="s">
         <v>21</v>
       </c>
       <c r="C233" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="D233" t="s">
         <v>33</v>
@@ -7631,13 +7634,13 @@
     </row>
     <row r="234" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B234" t="s">
         <v>21</v>
       </c>
       <c r="C234" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="D234" t="s">
         <v>33</v>
@@ -7648,13 +7651,13 @@
     </row>
     <row r="235" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B235" t="s">
         <v>21</v>
       </c>
       <c r="C235" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="D235" t="s">
         <v>33</v>
@@ -7665,13 +7668,13 @@
     </row>
     <row r="236" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B236" t="s">
         <v>21</v>
       </c>
       <c r="C236" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="D236" t="s">
         <v>33</v>
@@ -7682,13 +7685,13 @@
     </row>
     <row r="237" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B237" t="s">
         <v>21</v>
       </c>
       <c r="C237" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D237" t="s">
         <v>33</v>
@@ -7699,13 +7702,13 @@
     </row>
     <row r="238" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B238" t="s">
         <v>21</v>
       </c>
       <c r="C238" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="D238" t="s">
         <v>33</v>
@@ -7716,13 +7719,13 @@
     </row>
     <row r="239" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B239" t="s">
         <v>21</v>
       </c>
       <c r="C239" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="D239" t="s">
         <v>33</v>
@@ -7733,13 +7736,13 @@
     </row>
     <row r="240" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B240" t="s">
         <v>21</v>
       </c>
       <c r="C240" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="D240" t="s">
         <v>33</v>
@@ -7750,13 +7753,13 @@
     </row>
     <row r="241" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B241" t="s">
         <v>21</v>
       </c>
       <c r="C241" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="D241" t="s">
         <v>33</v>
@@ -7767,13 +7770,13 @@
     </row>
     <row r="242" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B242" t="s">
         <v>21</v>
       </c>
       <c r="C242" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="D242" t="s">
         <v>33</v>
@@ -7784,13 +7787,13 @@
     </row>
     <row r="243" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B243" t="s">
         <v>21</v>
       </c>
       <c r="C243" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="D243" t="s">
         <v>33</v>
@@ -7801,13 +7804,13 @@
     </row>
     <row r="244" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B244" t="s">
         <v>21</v>
       </c>
       <c r="C244" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="D244" t="s">
         <v>33</v>
@@ -7818,13 +7821,13 @@
     </row>
     <row r="245" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B245" t="s">
         <v>21</v>
       </c>
       <c r="C245" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="D245" t="s">
         <v>33</v>
@@ -7835,13 +7838,13 @@
     </row>
     <row r="246" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B246" t="s">
         <v>21</v>
       </c>
       <c r="C246" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="D246" t="s">
         <v>33</v>
@@ -7852,13 +7855,13 @@
     </row>
     <row r="247" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B247" t="s">
         <v>21</v>
       </c>
       <c r="C247" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="D247" t="s">
         <v>33</v>
@@ -7869,13 +7872,13 @@
     </row>
     <row r="248" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B248" t="s">
         <v>21</v>
       </c>
       <c r="C248" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="D248" t="s">
         <v>33</v>
@@ -7886,13 +7889,13 @@
     </row>
     <row r="249" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B249" t="s">
         <v>21</v>
       </c>
       <c r="C249" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="D249" t="s">
         <v>33</v>
@@ -7903,13 +7906,13 @@
     </row>
     <row r="250" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B250" t="s">
         <v>21</v>
       </c>
       <c r="C250" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="D250" t="s">
         <v>33</v>
@@ -7920,13 +7923,13 @@
     </row>
     <row r="251" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B251" t="s">
         <v>21</v>
       </c>
       <c r="C251" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="D251" t="s">
         <v>33</v>
@@ -7937,13 +7940,13 @@
     </row>
     <row r="252" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B252" t="s">
         <v>22</v>
       </c>
       <c r="C252" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="D252" t="s">
         <v>33</v>
@@ -7954,13 +7957,13 @@
     </row>
     <row r="253" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B253" t="s">
         <v>22</v>
       </c>
       <c r="C253" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="D253" t="s">
         <v>33</v>
@@ -7971,13 +7974,13 @@
     </row>
     <row r="254" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B254" t="s">
         <v>22</v>
       </c>
       <c r="C254" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="D254" t="s">
         <v>33</v>
@@ -7988,13 +7991,13 @@
     </row>
     <row r="255" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B255" t="s">
         <v>22</v>
       </c>
       <c r="C255" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="D255" t="s">
         <v>33</v>
@@ -8005,13 +8008,13 @@
     </row>
     <row r="256" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B256" t="s">
         <v>22</v>
       </c>
       <c r="C256" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="D256" t="s">
         <v>33</v>
@@ -8022,13 +8025,13 @@
     </row>
     <row r="257" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B257" t="s">
         <v>22</v>
       </c>
       <c r="C257" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="D257" t="s">
         <v>33</v>
@@ -8039,13 +8042,13 @@
     </row>
     <row r="258" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B258" t="s">
         <v>22</v>
       </c>
       <c r="C258" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D258" t="s">
         <v>33</v>
@@ -8056,13 +8059,13 @@
     </row>
     <row r="259" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B259" t="s">
         <v>22</v>
       </c>
       <c r="C259" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="D259" t="s">
         <v>33</v>
@@ -8073,13 +8076,13 @@
     </row>
     <row r="260" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B260" t="s">
         <v>22</v>
       </c>
       <c r="C260" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="D260" t="s">
         <v>33</v>
@@ -8090,13 +8093,13 @@
     </row>
     <row r="261" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B261" t="s">
         <v>22</v>
       </c>
       <c r="C261" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="D261" t="s">
         <v>33</v>
@@ -8107,13 +8110,13 @@
     </row>
     <row r="262" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B262" t="s">
         <v>22</v>
       </c>
       <c r="C262" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="D262" t="s">
         <v>33</v>
@@ -8124,13 +8127,13 @@
     </row>
     <row r="263" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B263" t="s">
         <v>22</v>
       </c>
       <c r="C263" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="D263" t="s">
         <v>33</v>
@@ -8141,13 +8144,13 @@
     </row>
     <row r="264" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B264" t="s">
         <v>22</v>
       </c>
       <c r="C264" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="D264" t="s">
         <v>33</v>
@@ -8158,13 +8161,13 @@
     </row>
     <row r="265" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B265" t="s">
         <v>22</v>
       </c>
       <c r="C265" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="D265" t="s">
         <v>33</v>
@@ -8175,13 +8178,13 @@
     </row>
     <row r="266" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B266" t="s">
         <v>22</v>
       </c>
       <c r="C266" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="D266" t="s">
         <v>33</v>
@@ -8192,13 +8195,13 @@
     </row>
     <row r="267" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B267" t="s">
         <v>22</v>
       </c>
       <c r="C267" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="D267" t="s">
         <v>33</v>
@@ -8209,13 +8212,13 @@
     </row>
     <row r="268" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B268" t="s">
         <v>22</v>
       </c>
       <c r="C268" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="D268" t="s">
         <v>33</v>
@@ -8226,13 +8229,13 @@
     </row>
     <row r="269" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B269" t="s">
         <v>22</v>
       </c>
       <c r="C269" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="D269" t="s">
         <v>33</v>
@@ -8243,13 +8246,13 @@
     </row>
     <row r="270" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B270" t="s">
         <v>22</v>
       </c>
       <c r="C270" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="D270" t="s">
         <v>33</v>
@@ -8260,13 +8263,13 @@
     </row>
     <row r="271" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B271" t="s">
         <v>22</v>
       </c>
       <c r="C271" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="D271" t="s">
         <v>33</v>
@@ -8277,13 +8280,13 @@
     </row>
     <row r="272" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B272" t="s">
         <v>22</v>
       </c>
       <c r="C272" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="D272" t="s">
         <v>33</v>
@@ -8294,13 +8297,13 @@
     </row>
     <row r="273" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B273" t="s">
         <v>22</v>
       </c>
       <c r="C273" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="D273" t="s">
         <v>33</v>
@@ -8311,13 +8314,13 @@
     </row>
     <row r="274" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B274" t="s">
         <v>22</v>
       </c>
       <c r="C274" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="D274" t="s">
         <v>33</v>
@@ -8328,13 +8331,13 @@
     </row>
     <row r="275" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B275" t="s">
         <v>22</v>
       </c>
       <c r="C275" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="D275" t="s">
         <v>33</v>
@@ -8345,13 +8348,13 @@
     </row>
     <row r="276" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B276" t="s">
         <v>22</v>
       </c>
       <c r="C276" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="D276" t="s">
         <v>33</v>
@@ -8362,13 +8365,13 @@
     </row>
     <row r="277" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B277" t="s">
         <v>22</v>
       </c>
       <c r="C277" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="D277" t="s">
         <v>33</v>
@@ -8379,13 +8382,13 @@
     </row>
     <row r="278" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B278" t="s">
         <v>22</v>
       </c>
       <c r="C278" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="D278" t="s">
         <v>33</v>
@@ -8396,13 +8399,13 @@
     </row>
     <row r="279" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B279" t="s">
         <v>22</v>
       </c>
       <c r="C279" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="D279" t="s">
         <v>33</v>
@@ -8413,13 +8416,13 @@
     </row>
     <row r="280" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B280" t="s">
         <v>22</v>
       </c>
       <c r="C280" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="D280" t="s">
         <v>33</v>
@@ -8430,13 +8433,13 @@
     </row>
     <row r="281" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B281" t="s">
         <v>22</v>
       </c>
       <c r="C281" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="D281" t="s">
         <v>33</v>
@@ -8447,13 +8450,13 @@
     </row>
     <row r="282" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B282" t="s">
         <v>22</v>
       </c>
       <c r="C282" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="D282" t="s">
         <v>33</v>
@@ -8464,13 +8467,13 @@
     </row>
     <row r="283" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B283" t="s">
         <v>22</v>
       </c>
       <c r="C283" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="D283" t="s">
         <v>33</v>
@@ -8481,13 +8484,13 @@
     </row>
     <row r="284" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B284" t="s">
         <v>22</v>
       </c>
       <c r="C284" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="D284" t="s">
         <v>33</v>
@@ -8498,13 +8501,13 @@
     </row>
     <row r="285" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B285" t="s">
         <v>22</v>
       </c>
       <c r="C285" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="D285" t="s">
         <v>33</v>
@@ -8515,13 +8518,13 @@
     </row>
     <row r="286" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B286" t="s">
         <v>22</v>
       </c>
       <c r="C286" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="D286" t="s">
         <v>33</v>
@@ -8532,13 +8535,13 @@
     </row>
     <row r="287" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B287" t="s">
         <v>22</v>
       </c>
       <c r="C287" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="D287" t="s">
         <v>33</v>
@@ -8549,13 +8552,13 @@
     </row>
     <row r="288" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="B288" t="s">
         <v>22</v>
       </c>
       <c r="C288" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="D288" t="s">
         <v>33</v>
@@ -8566,13 +8569,13 @@
     </row>
     <row r="289" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B289" t="s">
         <v>22</v>
       </c>
       <c r="C289" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="D289" t="s">
         <v>33</v>
@@ -8583,13 +8586,13 @@
     </row>
     <row r="290" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B290" t="s">
         <v>22</v>
       </c>
       <c r="C290" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="D290" t="s">
         <v>33</v>
@@ -8600,13 +8603,13 @@
     </row>
     <row r="291" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B291" t="s">
         <v>22</v>
       </c>
       <c r="C291" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="D291" t="s">
         <v>33</v>
@@ -8617,13 +8620,13 @@
     </row>
     <row r="292" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B292" t="s">
         <v>22</v>
       </c>
       <c r="C292" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="D292" t="s">
         <v>33</v>
@@ -8634,13 +8637,13 @@
     </row>
     <row r="293" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B293" t="s">
         <v>22</v>
       </c>
       <c r="C293" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="D293" t="s">
         <v>33</v>
@@ -8651,13 +8654,13 @@
     </row>
     <row r="294" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B294" t="s">
         <v>22</v>
       </c>
       <c r="C294" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="D294" t="s">
         <v>33</v>
@@ -8668,13 +8671,13 @@
     </row>
     <row r="295" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B295" t="s">
         <v>22</v>
       </c>
       <c r="C295" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="D295" t="s">
         <v>33</v>
@@ -8685,13 +8688,13 @@
     </row>
     <row r="296" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B296" t="s">
         <v>22</v>
       </c>
       <c r="C296" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="D296" t="s">
         <v>33</v>
@@ -8702,13 +8705,13 @@
     </row>
     <row r="297" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="B297" t="s">
         <v>22</v>
       </c>
       <c r="C297" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="D297" t="s">
         <v>33</v>
@@ -8719,13 +8722,13 @@
     </row>
     <row r="298" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B298" t="s">
         <v>22</v>
       </c>
       <c r="C298" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="D298" t="s">
         <v>33</v>
@@ -8736,13 +8739,13 @@
     </row>
     <row r="299" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B299" t="s">
         <v>22</v>
       </c>
       <c r="C299" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="D299" t="s">
         <v>33</v>
@@ -8753,13 +8756,13 @@
     </row>
     <row r="300" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="B300" t="s">
         <v>22</v>
       </c>
       <c r="C300" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="D300" t="s">
         <v>33</v>
@@ -8770,13 +8773,13 @@
     </row>
     <row r="301" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B301" t="s">
         <v>22</v>
       </c>
       <c r="C301" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="D301" t="s">
         <v>33</v>
@@ -8787,13 +8790,13 @@
     </row>
     <row r="302" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B302" t="s">
         <v>23</v>
       </c>
       <c r="C302" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="D302" t="s">
         <v>33</v>
@@ -8804,13 +8807,13 @@
     </row>
     <row r="303" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B303" t="s">
         <v>23</v>
       </c>
       <c r="C303" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="D303" t="s">
         <v>33</v>
@@ -8821,13 +8824,13 @@
     </row>
     <row r="304" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B304" t="s">
         <v>23</v>
       </c>
       <c r="C304" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="D304" t="s">
         <v>33</v>
@@ -8838,13 +8841,13 @@
     </row>
     <row r="305" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="B305" t="s">
         <v>23</v>
       </c>
       <c r="C305" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="D305" t="s">
         <v>33</v>
@@ -8855,13 +8858,13 @@
     </row>
     <row r="306" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="B306" t="s">
         <v>23</v>
       </c>
       <c r="C306" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="D306" t="s">
         <v>33</v>
@@ -8872,13 +8875,13 @@
     </row>
     <row r="307" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B307" t="s">
         <v>23</v>
       </c>
       <c r="C307" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="D307" t="s">
         <v>33</v>
@@ -8889,13 +8892,13 @@
     </row>
     <row r="308" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B308" t="s">
         <v>23</v>
       </c>
       <c r="C308" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="D308" t="s">
         <v>33</v>
@@ -8906,13 +8909,13 @@
     </row>
     <row r="309" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B309" t="s">
         <v>23</v>
       </c>
       <c r="C309" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="D309" t="s">
         <v>33</v>
@@ -8923,13 +8926,13 @@
     </row>
     <row r="310" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B310" t="s">
         <v>23</v>
       </c>
       <c r="C310" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="D310" t="s">
         <v>33</v>
@@ -8940,13 +8943,13 @@
     </row>
     <row r="311" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B311" t="s">
         <v>23</v>
       </c>
       <c r="C311" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="D311" t="s">
         <v>33</v>
@@ -8957,13 +8960,13 @@
     </row>
     <row r="312" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="B312" t="s">
         <v>23</v>
       </c>
       <c r="C312" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="D312" t="s">
         <v>33</v>
@@ -8974,13 +8977,13 @@
     </row>
     <row r="313" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B313" t="s">
         <v>23</v>
       </c>
       <c r="C313" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="D313" t="s">
         <v>33</v>
@@ -8991,13 +8994,13 @@
     </row>
     <row r="314" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="B314" t="s">
         <v>23</v>
       </c>
       <c r="C314" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="D314" t="s">
         <v>33</v>
@@ -9008,13 +9011,13 @@
     </row>
     <row r="315" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="B315" t="s">
         <v>23</v>
       </c>
       <c r="C315" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="D315" t="s">
         <v>33</v>
@@ -9025,13 +9028,13 @@
     </row>
     <row r="316" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="B316" t="s">
         <v>23</v>
       </c>
       <c r="C316" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="D316" t="s">
         <v>33</v>
@@ -9042,13 +9045,13 @@
     </row>
     <row r="317" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B317" t="s">
         <v>23</v>
       </c>
       <c r="C317" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="D317" t="s">
         <v>33</v>
@@ -9059,13 +9062,13 @@
     </row>
     <row r="318" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="B318" t="s">
         <v>23</v>
       </c>
       <c r="C318" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="D318" t="s">
         <v>33</v>
@@ -9076,13 +9079,13 @@
     </row>
     <row r="319" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="B319" t="s">
         <v>23</v>
       </c>
       <c r="C319" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="D319" t="s">
         <v>33</v>
@@ -9093,13 +9096,13 @@
     </row>
     <row r="320" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="B320" t="s">
         <v>23</v>
       </c>
       <c r="C320" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="D320" t="s">
         <v>33</v>
@@ -9110,13 +9113,13 @@
     </row>
     <row r="321" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="B321" t="s">
         <v>23</v>
       </c>
       <c r="C321" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="D321" t="s">
         <v>33</v>
@@ -9127,13 +9130,13 @@
     </row>
     <row r="322" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="B322" t="s">
         <v>23</v>
       </c>
       <c r="C322" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="D322" t="s">
         <v>33</v>
@@ -9144,13 +9147,13 @@
     </row>
     <row r="323" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="B323" t="s">
         <v>23</v>
       </c>
       <c r="C323" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="D323" t="s">
         <v>33</v>
@@ -9161,13 +9164,13 @@
     </row>
     <row r="324" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="B324" t="s">
         <v>23</v>
       </c>
       <c r="C324" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="D324" t="s">
         <v>33</v>
@@ -9178,13 +9181,13 @@
     </row>
     <row r="325" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="B325" t="s">
         <v>23</v>
       </c>
       <c r="C325" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="D325" t="s">
         <v>33</v>
@@ -9195,13 +9198,13 @@
     </row>
     <row r="326" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="B326" t="s">
         <v>23</v>
       </c>
       <c r="C326" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="D326" t="s">
         <v>33</v>
@@ -9212,13 +9215,13 @@
     </row>
     <row r="327" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="B327" t="s">
         <v>23</v>
       </c>
       <c r="C327" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="D327" t="s">
         <v>33</v>
@@ -9229,13 +9232,13 @@
     </row>
     <row r="328" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="B328" t="s">
         <v>23</v>
       </c>
       <c r="C328" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="D328" t="s">
         <v>33</v>
@@ -9246,13 +9249,13 @@
     </row>
     <row r="329" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="B329" t="s">
         <v>23</v>
       </c>
       <c r="C329" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="D329" t="s">
         <v>33</v>
@@ -9263,13 +9266,13 @@
     </row>
     <row r="330" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="B330" t="s">
         <v>23</v>
       </c>
       <c r="C330" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="D330" t="s">
         <v>33</v>
@@ -9280,13 +9283,13 @@
     </row>
     <row r="331" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="B331" t="s">
         <v>23</v>
       </c>
       <c r="C331" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="D331" t="s">
         <v>33</v>
@@ -9297,13 +9300,13 @@
     </row>
     <row r="332" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="B332" t="s">
         <v>23</v>
       </c>
       <c r="C332" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="D332" t="s">
         <v>33</v>
@@ -9314,13 +9317,13 @@
     </row>
     <row r="333" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="B333" t="s">
         <v>23</v>
       </c>
       <c r="C333" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="D333" t="s">
         <v>33</v>
@@ -9331,13 +9334,13 @@
     </row>
     <row r="334" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="B334" t="s">
         <v>23</v>
       </c>
       <c r="C334" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="D334" t="s">
         <v>33</v>
@@ -9348,13 +9351,13 @@
     </row>
     <row r="335" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="B335" t="s">
         <v>23</v>
       </c>
       <c r="C335" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="D335" t="s">
         <v>33</v>
@@ -9365,13 +9368,13 @@
     </row>
     <row r="336" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="B336" t="s">
         <v>23</v>
       </c>
       <c r="C336" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="D336" t="s">
         <v>33</v>
@@ -9382,13 +9385,13 @@
     </row>
     <row r="337" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="B337" t="s">
         <v>23</v>
       </c>
       <c r="C337" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="D337" t="s">
         <v>33</v>
@@ -9399,13 +9402,13 @@
     </row>
     <row r="338" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="B338" t="s">
         <v>23</v>
       </c>
       <c r="C338" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="D338" t="s">
         <v>33</v>
@@ -9416,13 +9419,13 @@
     </row>
     <row r="339" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B339" t="s">
         <v>23</v>
       </c>
       <c r="C339" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="D339" t="s">
         <v>33</v>
@@ -9433,13 +9436,13 @@
     </row>
     <row r="340" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="B340" t="s">
         <v>23</v>
       </c>
       <c r="C340" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="D340" t="s">
         <v>33</v>
@@ -9450,13 +9453,13 @@
     </row>
     <row r="341" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="B341" t="s">
         <v>23</v>
       </c>
       <c r="C341" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="D341" t="s">
         <v>33</v>
@@ -9467,13 +9470,13 @@
     </row>
     <row r="342" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="B342" t="s">
         <v>23</v>
       </c>
       <c r="C342" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="D342" t="s">
         <v>33</v>
@@ -9484,13 +9487,13 @@
     </row>
     <row r="343" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="B343" t="s">
         <v>23</v>
       </c>
       <c r="C343" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="D343" t="s">
         <v>33</v>
@@ -9501,13 +9504,13 @@
     </row>
     <row r="344" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="B344" t="s">
         <v>23</v>
       </c>
       <c r="C344" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="D344" t="s">
         <v>33</v>
@@ -9518,13 +9521,13 @@
     </row>
     <row r="345" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="B345" t="s">
         <v>23</v>
       </c>
       <c r="C345" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="D345" t="s">
         <v>33</v>
@@ -9535,13 +9538,13 @@
     </row>
     <row r="346" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="B346" t="s">
         <v>23</v>
       </c>
       <c r="C346" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="D346" t="s">
         <v>33</v>
@@ -9552,13 +9555,13 @@
     </row>
     <row r="347" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="B347" t="s">
         <v>23</v>
       </c>
       <c r="C347" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="D347" t="s">
         <v>33</v>
@@ -9569,13 +9572,13 @@
     </row>
     <row r="348" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="B348" t="s">
         <v>23</v>
       </c>
       <c r="C348" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="D348" t="s">
         <v>33</v>
@@ -9586,13 +9589,13 @@
     </row>
     <row r="349" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B349" t="s">
         <v>23</v>
       </c>
       <c r="C349" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="D349" t="s">
         <v>33</v>
@@ -9603,13 +9606,13 @@
     </row>
     <row r="350" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B350" t="s">
         <v>23</v>
       </c>
       <c r="C350" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="D350" t="s">
         <v>33</v>
@@ -9620,13 +9623,13 @@
     </row>
     <row r="351" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="B351" t="s">
         <v>23</v>
       </c>
       <c r="C351" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="D351" t="s">
         <v>33</v>
@@ -9637,13 +9640,13 @@
     </row>
     <row r="352" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="B352" t="s">
         <v>24</v>
       </c>
       <c r="C352" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="D352" t="s">
         <v>33</v>
@@ -9654,13 +9657,13 @@
     </row>
     <row r="353" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="B353" t="s">
         <v>24</v>
       </c>
       <c r="C353" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="D353" t="s">
         <v>33</v>
@@ -9671,13 +9674,13 @@
     </row>
     <row r="354" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="B354" t="s">
         <v>24</v>
       </c>
       <c r="C354" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="D354" t="s">
         <v>33</v>
@@ -9688,13 +9691,13 @@
     </row>
     <row r="355" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="B355" t="s">
         <v>24</v>
       </c>
       <c r="C355" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="D355" t="s">
         <v>33</v>
@@ -9705,13 +9708,13 @@
     </row>
     <row r="356" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="B356" t="s">
         <v>24</v>
       </c>
       <c r="C356" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="D356" t="s">
         <v>33</v>
@@ -9722,13 +9725,13 @@
     </row>
     <row r="357" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="B357" t="s">
         <v>24</v>
       </c>
       <c r="C357" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="D357" t="s">
         <v>33</v>
@@ -9739,13 +9742,13 @@
     </row>
     <row r="358" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="B358" t="s">
         <v>24</v>
       </c>
       <c r="C358" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="D358" t="s">
         <v>33</v>
@@ -9756,13 +9759,13 @@
     </row>
     <row r="359" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="B359" t="s">
         <v>24</v>
       </c>
       <c r="C359" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="D359" t="s">
         <v>33</v>
@@ -9773,13 +9776,13 @@
     </row>
     <row r="360" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="B360" t="s">
         <v>24</v>
       </c>
       <c r="C360" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="D360" t="s">
         <v>33</v>
@@ -9790,13 +9793,13 @@
     </row>
     <row r="361" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="B361" t="s">
         <v>24</v>
       </c>
       <c r="C361" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="D361" t="s">
         <v>33</v>
@@ -9807,13 +9810,13 @@
     </row>
     <row r="362" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="B362" t="s">
         <v>24</v>
       </c>
       <c r="C362" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="D362" t="s">
         <v>33</v>
@@ -9824,13 +9827,13 @@
     </row>
     <row r="363" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="B363" t="s">
         <v>24</v>
       </c>
       <c r="C363" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="D363" t="s">
         <v>33</v>
@@ -9841,13 +9844,13 @@
     </row>
     <row r="364" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="B364" t="s">
         <v>24</v>
       </c>
       <c r="C364" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="D364" t="s">
         <v>33</v>
@@ -9858,13 +9861,13 @@
     </row>
     <row r="365" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="B365" t="s">
         <v>24</v>
       </c>
       <c r="C365" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="D365" t="s">
         <v>33</v>
@@ -9875,13 +9878,13 @@
     </row>
     <row r="366" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="B366" t="s">
         <v>24</v>
       </c>
       <c r="C366" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="D366" t="s">
         <v>33</v>
@@ -9892,13 +9895,13 @@
     </row>
     <row r="367" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="B367" t="s">
         <v>24</v>
       </c>
       <c r="C367" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="D367" t="s">
         <v>33</v>
@@ -9909,13 +9912,13 @@
     </row>
     <row r="368" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="B368" t="s">
         <v>24</v>
       </c>
       <c r="C368" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="D368" t="s">
         <v>33</v>
@@ -9926,13 +9929,13 @@
     </row>
     <row r="369" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="B369" t="s">
         <v>24</v>
       </c>
       <c r="C369" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="D369" t="s">
         <v>33</v>
@@ -9943,13 +9946,13 @@
     </row>
     <row r="370" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="B370" t="s">
         <v>24</v>
       </c>
       <c r="C370" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="D370" t="s">
         <v>33</v>
@@ -9960,13 +9963,13 @@
     </row>
     <row r="371" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="B371" t="s">
         <v>24</v>
       </c>
       <c r="C371" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="D371" t="s">
         <v>33</v>
@@ -9977,13 +9980,13 @@
     </row>
     <row r="372" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="B372" t="s">
         <v>24</v>
       </c>
       <c r="C372" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="D372" t="s">
         <v>33</v>
@@ -9994,13 +9997,13 @@
     </row>
     <row r="373" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="B373" t="s">
         <v>24</v>
       </c>
       <c r="C373" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="D373" t="s">
         <v>33</v>
@@ -10011,13 +10014,13 @@
     </row>
     <row r="374" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="B374" t="s">
         <v>24</v>
       </c>
       <c r="C374" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="D374" t="s">
         <v>33</v>
@@ -10028,13 +10031,13 @@
     </row>
     <row r="375" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="B375" t="s">
         <v>24</v>
       </c>
       <c r="C375" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="D375" t="s">
         <v>33</v>
@@ -10045,13 +10048,13 @@
     </row>
     <row r="376" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="B376" t="s">
         <v>24</v>
       </c>
       <c r="C376" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="D376" t="s">
         <v>33</v>
@@ -10062,13 +10065,13 @@
     </row>
     <row r="377" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="B377" t="s">
         <v>24</v>
       </c>
       <c r="C377" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="D377" t="s">
         <v>33</v>
@@ -10079,13 +10082,13 @@
     </row>
     <row r="378" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="B378" t="s">
         <v>24</v>
       </c>
       <c r="C378" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="D378" t="s">
         <v>33</v>
@@ -10096,13 +10099,13 @@
     </row>
     <row r="379" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="B379" t="s">
         <v>24</v>
       </c>
       <c r="C379" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="D379" t="s">
         <v>33</v>
@@ -10113,13 +10116,13 @@
     </row>
     <row r="380" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="B380" t="s">
         <v>24</v>
       </c>
       <c r="C380" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="D380" t="s">
         <v>33</v>
@@ -10130,13 +10133,13 @@
     </row>
     <row r="381" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="B381" t="s">
         <v>24</v>
       </c>
       <c r="C381" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="D381" t="s">
         <v>33</v>
@@ -10147,13 +10150,13 @@
     </row>
     <row r="382" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="B382" t="s">
         <v>24</v>
       </c>
       <c r="C382" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="D382" t="s">
         <v>33</v>
@@ -10164,13 +10167,13 @@
     </row>
     <row r="383" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="B383" t="s">
         <v>24</v>
       </c>
       <c r="C383" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="D383" t="s">
         <v>33</v>
@@ -10181,13 +10184,13 @@
     </row>
     <row r="384" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="B384" t="s">
         <v>24</v>
       </c>
       <c r="C384" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="D384" t="s">
         <v>33</v>
@@ -10198,13 +10201,13 @@
     </row>
     <row r="385" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="B385" t="s">
         <v>24</v>
       </c>
       <c r="C385" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="D385" t="s">
         <v>33</v>
@@ -10215,13 +10218,13 @@
     </row>
     <row r="386" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="B386" t="s">
         <v>24</v>
       </c>
       <c r="C386" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="D386" t="s">
         <v>33</v>
@@ -10232,13 +10235,13 @@
     </row>
     <row r="387" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="B387" t="s">
         <v>24</v>
       </c>
       <c r="C387" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="D387" t="s">
         <v>33</v>
@@ -10249,13 +10252,13 @@
     </row>
     <row r="388" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="B388" t="s">
         <v>24</v>
       </c>
       <c r="C388" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="D388" t="s">
         <v>33</v>
@@ -10266,13 +10269,13 @@
     </row>
     <row r="389" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="B389" t="s">
         <v>24</v>
       </c>
       <c r="C389" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="D389" t="s">
         <v>33</v>
@@ -10283,13 +10286,13 @@
     </row>
     <row r="390" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="B390" t="s">
         <v>24</v>
       </c>
       <c r="C390" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="D390" t="s">
         <v>33</v>
@@ -10300,13 +10303,13 @@
     </row>
     <row r="391" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="B391" t="s">
         <v>24</v>
       </c>
       <c r="C391" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="D391" t="s">
         <v>33</v>
@@ -10317,13 +10320,13 @@
     </row>
     <row r="392" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B392" t="s">
         <v>24</v>
       </c>
       <c r="C392" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="D392" t="s">
         <v>33</v>
@@ -10334,13 +10337,13 @@
     </row>
     <row r="393" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="B393" t="s">
         <v>24</v>
       </c>
       <c r="C393" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="D393" t="s">
         <v>33</v>
@@ -10351,13 +10354,13 @@
     </row>
     <row r="394" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="B394" t="s">
         <v>24</v>
       </c>
       <c r="C394" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="D394" t="s">
         <v>33</v>
@@ -10368,13 +10371,13 @@
     </row>
     <row r="395" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="B395" t="s">
         <v>24</v>
       </c>
       <c r="C395" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="D395" t="s">
         <v>33</v>
@@ -10385,13 +10388,13 @@
     </row>
     <row r="396" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="B396" t="s">
         <v>24</v>
       </c>
       <c r="C396" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="D396" t="s">
         <v>33</v>
@@ -10402,13 +10405,13 @@
     </row>
     <row r="397" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="B397" t="s">
         <v>24</v>
       </c>
       <c r="C397" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D397" t="s">
         <v>33</v>
@@ -10419,13 +10422,13 @@
     </row>
     <row r="398" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="B398" t="s">
         <v>24</v>
       </c>
       <c r="C398" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="D398" t="s">
         <v>33</v>
@@ -10436,13 +10439,13 @@
     </row>
     <row r="399" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="B399" t="s">
         <v>24</v>
       </c>
       <c r="C399" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="D399" t="s">
         <v>33</v>
@@ -10453,13 +10456,13 @@
     </row>
     <row r="400" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="B400" t="s">
         <v>24</v>
       </c>
       <c r="C400" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="D400" t="s">
         <v>33</v>
@@ -10470,13 +10473,13 @@
     </row>
     <row r="401" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="B401" t="s">
         <v>24</v>
       </c>
       <c r="C401" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="D401" t="s">
         <v>33</v>
@@ -10487,13 +10490,13 @@
     </row>
     <row r="402" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="B402" t="s">
         <v>25</v>
       </c>
       <c r="C402" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="D402" t="s">
         <v>33</v>
@@ -10504,13 +10507,13 @@
     </row>
     <row r="403" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="B403" t="s">
         <v>25</v>
       </c>
       <c r="C403" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="D403" t="s">
         <v>33</v>
@@ -10521,13 +10524,13 @@
     </row>
     <row r="404" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="B404" t="s">
         <v>25</v>
       </c>
       <c r="C404" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="D404" t="s">
         <v>33</v>
@@ -10538,13 +10541,13 @@
     </row>
     <row r="405" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B405" t="s">
         <v>25</v>
       </c>
       <c r="C405" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="D405" t="s">
         <v>33</v>
@@ -10555,13 +10558,13 @@
     </row>
     <row r="406" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="B406" t="s">
         <v>25</v>
       </c>
       <c r="C406" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="D406" t="s">
         <v>33</v>
@@ -10572,13 +10575,13 @@
     </row>
     <row r="407" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B407" t="s">
         <v>25</v>
       </c>
       <c r="C407" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="D407" t="s">
         <v>33</v>
@@ -10589,13 +10592,13 @@
     </row>
     <row r="408" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="B408" t="s">
         <v>25</v>
       </c>
       <c r="C408" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="D408" t="s">
         <v>33</v>
@@ -10606,13 +10609,13 @@
     </row>
     <row r="409" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="B409" t="s">
         <v>25</v>
       </c>
       <c r="C409" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="D409" t="s">
         <v>33</v>
@@ -10623,13 +10626,13 @@
     </row>
     <row r="410" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="B410" t="s">
         <v>25</v>
       </c>
       <c r="C410" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="D410" t="s">
         <v>33</v>
@@ -10640,13 +10643,13 @@
     </row>
     <row r="411" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="B411" t="s">
         <v>25</v>
       </c>
       <c r="C411" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="D411" t="s">
         <v>33</v>
@@ -10657,13 +10660,13 @@
     </row>
     <row r="412" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="B412" t="s">
         <v>25</v>
       </c>
       <c r="C412" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="D412" t="s">
         <v>33</v>
@@ -10674,13 +10677,13 @@
     </row>
     <row r="413" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="B413" t="s">
         <v>25</v>
       </c>
       <c r="C413" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="D413" t="s">
         <v>33</v>
@@ -10691,13 +10694,13 @@
     </row>
     <row r="414" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="B414" t="s">
         <v>25</v>
       </c>
       <c r="C414" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="D414" t="s">
         <v>33</v>
@@ -10708,13 +10711,13 @@
     </row>
     <row r="415" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="B415" t="s">
         <v>25</v>
       </c>
       <c r="C415" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="D415" t="s">
         <v>33</v>
@@ -10725,13 +10728,13 @@
     </row>
     <row r="416" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="B416" t="s">
         <v>25</v>
       </c>
       <c r="C416" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="D416" t="s">
         <v>33</v>
@@ -10742,13 +10745,13 @@
     </row>
     <row r="417" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="B417" t="s">
         <v>25</v>
       </c>
       <c r="C417" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="D417" t="s">
         <v>33</v>
@@ -10759,13 +10762,13 @@
     </row>
     <row r="418" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="B418" t="s">
         <v>25</v>
       </c>
       <c r="C418" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="D418" t="s">
         <v>33</v>
@@ -10776,13 +10779,13 @@
     </row>
     <row r="419" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="B419" t="s">
         <v>25</v>
       </c>
       <c r="C419" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="D419" t="s">
         <v>33</v>
@@ -10793,13 +10796,13 @@
     </row>
     <row r="420" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="B420" t="s">
         <v>25</v>
       </c>
       <c r="C420" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="D420" t="s">
         <v>33</v>
@@ -10810,13 +10813,13 @@
     </row>
     <row r="421" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="B421" t="s">
         <v>25</v>
       </c>
       <c r="C421" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="D421" t="s">
         <v>33</v>
@@ -10827,13 +10830,13 @@
     </row>
     <row r="422" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B422" t="s">
         <v>25</v>
       </c>
       <c r="C422" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="D422" t="s">
         <v>33</v>
@@ -10844,13 +10847,13 @@
     </row>
     <row r="423" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="B423" t="s">
         <v>25</v>
       </c>
       <c r="C423" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="D423" t="s">
         <v>33</v>
@@ -10861,13 +10864,13 @@
     </row>
     <row r="424" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="B424" t="s">
         <v>25</v>
       </c>
       <c r="C424" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="D424" t="s">
         <v>33</v>
@@ -10878,13 +10881,13 @@
     </row>
     <row r="425" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="B425" t="s">
         <v>25</v>
       </c>
       <c r="C425" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="D425" t="s">
         <v>33</v>
@@ -10895,13 +10898,13 @@
     </row>
     <row r="426" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="B426" t="s">
         <v>25</v>
       </c>
       <c r="C426" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="D426" t="s">
         <v>33</v>
@@ -10912,13 +10915,13 @@
     </row>
     <row r="427" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="B427" t="s">
         <v>25</v>
       </c>
       <c r="C427" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="D427" t="s">
         <v>33</v>
@@ -10929,13 +10932,13 @@
     </row>
     <row r="428" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="B428" t="s">
         <v>25</v>
       </c>
       <c r="C428" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="D428" t="s">
         <v>33</v>
@@ -10946,13 +10949,13 @@
     </row>
     <row r="429" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="B429" t="s">
         <v>25</v>
       </c>
       <c r="C429" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="D429" t="s">
         <v>33</v>
@@ -10963,13 +10966,13 @@
     </row>
     <row r="430" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="B430" t="s">
         <v>25</v>
       </c>
       <c r="C430" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="D430" t="s">
         <v>33</v>
@@ -10980,13 +10983,13 @@
     </row>
     <row r="431" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="B431" t="s">
         <v>25</v>
       </c>
       <c r="C431" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="D431" t="s">
         <v>33</v>
@@ -10997,13 +11000,13 @@
     </row>
     <row r="432" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="B432" t="s">
         <v>25</v>
       </c>
       <c r="C432" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="D432" t="s">
         <v>33</v>
@@ -11014,13 +11017,13 @@
     </row>
     <row r="433" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="B433" t="s">
         <v>25</v>
       </c>
       <c r="C433" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="D433" t="s">
         <v>33</v>
@@ -11031,13 +11034,13 @@
     </row>
     <row r="434" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="B434" t="s">
         <v>25</v>
       </c>
       <c r="C434" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="D434" t="s">
         <v>33</v>
@@ -11048,13 +11051,13 @@
     </row>
     <row r="435" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="B435" t="s">
         <v>25</v>
       </c>
       <c r="C435" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="D435" t="s">
         <v>33</v>
@@ -11065,13 +11068,13 @@
     </row>
     <row r="436" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="B436" t="s">
         <v>25</v>
       </c>
       <c r="C436" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="D436" t="s">
         <v>33</v>
@@ -11082,13 +11085,13 @@
     </row>
     <row r="437" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="B437" t="s">
         <v>25</v>
       </c>
       <c r="C437" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="D437" t="s">
         <v>33</v>
@@ -11099,13 +11102,13 @@
     </row>
     <row r="438" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="B438" t="s">
         <v>25</v>
       </c>
       <c r="C438" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="D438" t="s">
         <v>33</v>
@@ -11116,13 +11119,13 @@
     </row>
     <row r="439" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="B439" t="s">
         <v>25</v>
       </c>
       <c r="C439" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="D439" t="s">
         <v>33</v>
@@ -11133,13 +11136,13 @@
     </row>
     <row r="440" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="B440" t="s">
         <v>25</v>
       </c>
       <c r="C440" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="D440" t="s">
         <v>33</v>
@@ -11150,13 +11153,13 @@
     </row>
     <row r="441" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="B441" t="s">
         <v>25</v>
       </c>
       <c r="C441" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="D441" t="s">
         <v>33</v>
@@ -11167,13 +11170,13 @@
     </row>
     <row r="442" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="B442" t="s">
         <v>25</v>
       </c>
       <c r="C442" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="D442" t="s">
         <v>33</v>
@@ -11184,13 +11187,13 @@
     </row>
     <row r="443" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="B443" t="s">
         <v>25</v>
       </c>
       <c r="C443" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="D443" t="s">
         <v>33</v>
@@ -11201,13 +11204,13 @@
     </row>
     <row r="444" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="B444" t="s">
         <v>25</v>
       </c>
       <c r="C444" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="D444" t="s">
         <v>33</v>
@@ -11218,13 +11221,13 @@
     </row>
     <row r="445" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="B445" t="s">
         <v>25</v>
       </c>
       <c r="C445" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="D445" t="s">
         <v>33</v>
@@ -11235,13 +11238,13 @@
     </row>
     <row r="446" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A446" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="B446" t="s">
         <v>25</v>
       </c>
       <c r="C446" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="D446" t="s">
         <v>33</v>
@@ -11252,13 +11255,13 @@
     </row>
     <row r="447" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="B447" t="s">
         <v>25</v>
       </c>
       <c r="C447" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="D447" t="s">
         <v>33</v>
@@ -11269,13 +11272,13 @@
     </row>
     <row r="448" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="B448" t="s">
         <v>25</v>
       </c>
       <c r="C448" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="D448" t="s">
         <v>33</v>
@@ -11286,13 +11289,13 @@
     </row>
     <row r="449" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="B449" t="s">
         <v>25</v>
       </c>
       <c r="C449" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="D449" t="s">
         <v>33</v>
@@ -11303,13 +11306,13 @@
     </row>
     <row r="450" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="B450" t="s">
         <v>25</v>
       </c>
       <c r="C450" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="D450" t="s">
         <v>33</v>
@@ -11320,13 +11323,13 @@
     </row>
     <row r="451" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="B451" t="s">
         <v>25</v>
       </c>
       <c r="C451" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="D451" t="s">
         <v>33</v>
@@ -11337,13 +11340,13 @@
     </row>
     <row r="452" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="B452" t="s">
         <v>26</v>
       </c>
       <c r="C452" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="D452" t="s">
         <v>33</v>
@@ -11354,13 +11357,13 @@
     </row>
     <row r="453" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="B453" t="s">
         <v>26</v>
       </c>
       <c r="C453" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="D453" t="s">
         <v>33</v>
@@ -11371,13 +11374,13 @@
     </row>
     <row r="454" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="B454" t="s">
         <v>26</v>
       </c>
       <c r="C454" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="D454" t="s">
         <v>33</v>
@@ -11388,13 +11391,13 @@
     </row>
     <row r="455" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="B455" t="s">
         <v>26</v>
       </c>
       <c r="C455" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="D455" t="s">
         <v>33</v>
@@ -11405,13 +11408,13 @@
     </row>
     <row r="456" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="B456" t="s">
         <v>26</v>
       </c>
       <c r="C456" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="D456" t="s">
         <v>33</v>
@@ -11422,13 +11425,13 @@
     </row>
     <row r="457" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="B457" t="s">
         <v>26</v>
       </c>
       <c r="C457" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="D457" t="s">
         <v>33</v>
@@ -11439,13 +11442,13 @@
     </row>
     <row r="458" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="B458" t="s">
         <v>26</v>
       </c>
       <c r="C458" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="D458" t="s">
         <v>33</v>
@@ -11456,13 +11459,13 @@
     </row>
     <row r="459" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="B459" t="s">
         <v>26</v>
       </c>
       <c r="C459" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="D459" t="s">
         <v>33</v>
@@ -11473,13 +11476,13 @@
     </row>
     <row r="460" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="B460" t="s">
         <v>26</v>
       </c>
       <c r="C460" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="D460" t="s">
         <v>33</v>
@@ -11490,13 +11493,13 @@
     </row>
     <row r="461" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="B461" t="s">
         <v>26</v>
       </c>
       <c r="C461" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="D461" t="s">
         <v>33</v>
@@ -11507,13 +11510,13 @@
     </row>
     <row r="462" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="B462" t="s">
         <v>26</v>
       </c>
       <c r="C462" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="D462" t="s">
         <v>33</v>
@@ -11524,13 +11527,13 @@
     </row>
     <row r="463" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="B463" t="s">
         <v>26</v>
       </c>
       <c r="C463" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="D463" t="s">
         <v>33</v>
@@ -11541,13 +11544,13 @@
     </row>
     <row r="464" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="B464" t="s">
         <v>26</v>
       </c>
       <c r="C464" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="D464" t="s">
         <v>33</v>
@@ -11558,13 +11561,13 @@
     </row>
     <row r="465" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="B465" t="s">
         <v>26</v>
       </c>
       <c r="C465" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="D465" t="s">
         <v>33</v>
@@ -11575,13 +11578,13 @@
     </row>
     <row r="466" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="B466" t="s">
         <v>26</v>
       </c>
       <c r="C466" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="D466" t="s">
         <v>33</v>
@@ -11592,13 +11595,13 @@
     </row>
     <row r="467" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="B467" t="s">
         <v>26</v>
       </c>
       <c r="C467" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="D467" t="s">
         <v>33</v>
@@ -11609,13 +11612,13 @@
     </row>
     <row r="468" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="B468" t="s">
         <v>26</v>
       </c>
       <c r="C468" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="D468" t="s">
         <v>33</v>
@@ -11626,13 +11629,13 @@
     </row>
     <row r="469" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A469" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="B469" t="s">
         <v>26</v>
       </c>
       <c r="C469" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="D469" t="s">
         <v>33</v>
@@ -11643,13 +11646,13 @@
     </row>
     <row r="470" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="B470" t="s">
         <v>26</v>
       </c>
       <c r="C470" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="D470" t="s">
         <v>33</v>
@@ -11660,13 +11663,13 @@
     </row>
     <row r="471" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A471" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="B471" t="s">
         <v>26</v>
       </c>
       <c r="C471" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="D471" t="s">
         <v>33</v>
@@ -11677,13 +11680,13 @@
     </row>
     <row r="472" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="B472" t="s">
         <v>26</v>
       </c>
       <c r="C472" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="D472" t="s">
         <v>33</v>
@@ -11694,13 +11697,13 @@
     </row>
     <row r="473" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="B473" t="s">
         <v>26</v>
       </c>
       <c r="C473" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="D473" t="s">
         <v>33</v>
@@ -11711,13 +11714,13 @@
     </row>
     <row r="474" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A474" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="B474" t="s">
         <v>26</v>
       </c>
       <c r="C474" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="D474" t="s">
         <v>33</v>
@@ -11728,13 +11731,13 @@
     </row>
     <row r="475" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="B475" t="s">
         <v>26</v>
       </c>
       <c r="C475" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="D475" t="s">
         <v>33</v>
@@ -11745,13 +11748,13 @@
     </row>
     <row r="476" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="B476" t="s">
         <v>26</v>
       </c>
       <c r="C476" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="D476" t="s">
         <v>33</v>
@@ -11762,13 +11765,13 @@
     </row>
     <row r="477" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="B477" t="s">
         <v>26</v>
       </c>
       <c r="C477" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="D477" t="s">
         <v>33</v>
@@ -11779,13 +11782,13 @@
     </row>
     <row r="478" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="B478" t="s">
         <v>26</v>
       </c>
       <c r="C478" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="D478" t="s">
         <v>33</v>
@@ -11796,13 +11799,13 @@
     </row>
     <row r="479" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="B479" t="s">
         <v>26</v>
       </c>
       <c r="C479" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="D479" t="s">
         <v>33</v>
@@ -11813,13 +11816,13 @@
     </row>
     <row r="480" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A480" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="B480" t="s">
         <v>26</v>
       </c>
       <c r="C480" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="D480" t="s">
         <v>33</v>
@@ -11830,13 +11833,13 @@
     </row>
     <row r="481" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A481" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="B481" t="s">
         <v>26</v>
       </c>
       <c r="C481" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="D481" t="s">
         <v>33</v>
@@ -11847,13 +11850,13 @@
     </row>
     <row r="482" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A482" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="B482" t="s">
         <v>26</v>
       </c>
       <c r="C482" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="D482" t="s">
         <v>33</v>
@@ -11864,13 +11867,13 @@
     </row>
     <row r="483" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A483" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="B483" t="s">
         <v>26</v>
       </c>
       <c r="C483" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="D483" t="s">
         <v>33</v>
@@ -11881,13 +11884,13 @@
     </row>
     <row r="484" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A484" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="B484" t="s">
         <v>26</v>
       </c>
       <c r="C484" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="D484" t="s">
         <v>33</v>
@@ -11898,13 +11901,13 @@
     </row>
     <row r="485" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A485" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="B485" t="s">
         <v>26</v>
       </c>
       <c r="C485" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="D485" t="s">
         <v>33</v>
@@ -11915,13 +11918,13 @@
     </row>
     <row r="486" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A486" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="B486" t="s">
         <v>26</v>
       </c>
       <c r="C486" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="D486" t="s">
         <v>33</v>
@@ -11932,13 +11935,13 @@
     </row>
     <row r="487" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A487" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="B487" t="s">
         <v>26</v>
       </c>
       <c r="C487" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="D487" t="s">
         <v>33</v>
@@ -11949,13 +11952,13 @@
     </row>
     <row r="488" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A488" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="B488" t="s">
         <v>26</v>
       </c>
       <c r="C488" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="D488" t="s">
         <v>33</v>
@@ -11966,13 +11969,13 @@
     </row>
     <row r="489" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A489" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="B489" t="s">
         <v>26</v>
       </c>
       <c r="C489" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="D489" t="s">
         <v>33</v>
@@ -11983,13 +11986,13 @@
     </row>
     <row r="490" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A490" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="B490" t="s">
         <v>26</v>
       </c>
       <c r="C490" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="D490" t="s">
         <v>33</v>
@@ -12000,13 +12003,13 @@
     </row>
     <row r="491" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A491" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="B491" t="s">
         <v>26</v>
       </c>
       <c r="C491" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="D491" t="s">
         <v>33</v>
@@ -12017,13 +12020,13 @@
     </row>
     <row r="492" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A492" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="B492" t="s">
         <v>26</v>
       </c>
       <c r="C492" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="D492" t="s">
         <v>33</v>
@@ -12034,13 +12037,13 @@
     </row>
     <row r="493" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A493" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B493" t="s">
         <v>26</v>
       </c>
       <c r="C493" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="D493" t="s">
         <v>33</v>
@@ -12051,13 +12054,13 @@
     </row>
     <row r="494" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A494" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="B494" t="s">
         <v>26</v>
       </c>
       <c r="C494" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="D494" t="s">
         <v>33</v>
@@ -12068,13 +12071,13 @@
     </row>
     <row r="495" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A495" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="B495" t="s">
         <v>26</v>
       </c>
       <c r="C495" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="D495" t="s">
         <v>33</v>
@@ -12085,13 +12088,13 @@
     </row>
     <row r="496" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A496" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="B496" t="s">
         <v>26</v>
       </c>
       <c r="C496" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="D496" t="s">
         <v>33</v>
@@ -12102,13 +12105,13 @@
     </row>
     <row r="497" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A497" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="B497" t="s">
         <v>26</v>
       </c>
       <c r="C497" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="D497" t="s">
         <v>33</v>
@@ -12119,13 +12122,13 @@
     </row>
     <row r="498" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A498" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="B498" t="s">
         <v>26</v>
       </c>
       <c r="C498" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="D498" t="s">
         <v>33</v>
@@ -12136,13 +12139,13 @@
     </row>
     <row r="499" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A499" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="B499" t="s">
         <v>26</v>
       </c>
       <c r="C499" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="D499" t="s">
         <v>33</v>
@@ -12153,13 +12156,13 @@
     </row>
     <row r="500" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A500" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="B500" t="s">
         <v>26</v>
       </c>
       <c r="C500" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="D500" t="s">
         <v>33</v>
@@ -12170,13 +12173,13 @@
     </row>
     <row r="501" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A501" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="B501" t="s">
         <v>26</v>
       </c>
       <c r="C501" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="D501" t="s">
         <v>33</v>
